--- a/data/umr/Resumen UMR Febrero 2026.xlsx
+++ b/data/umr/Resumen UMR Febrero 2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C79EC4-D17A-4F36-9FD3-7872D5DBF80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{02C79EC4-D17A-4F36-9FD3-7872D5DBF80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE3628A8-1D6A-407F-8578-8F7690224D30}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Odometro-Kilometraje" sheetId="1" r:id="rId1"/>
@@ -3604,7 +3604,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="85" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="85" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="59" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3620,9 +3674,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3649,48 +3700,6 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="59" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -3703,6 +3712,9 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3730,18 +3742,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="60" borderId="85" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="61" borderId="85" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -4765,37 +4765,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="334" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="334"/>
-      <c r="C1" s="334"/>
-      <c r="D1" s="334"/>
-      <c r="E1" s="334"/>
-      <c r="F1" s="334"/>
-      <c r="G1" s="334"/>
-      <c r="H1" s="334"/>
-      <c r="I1" s="334"/>
-      <c r="J1" s="334"/>
-      <c r="K1" s="334"/>
-      <c r="L1" s="334"/>
-      <c r="M1" s="334"/>
-      <c r="N1" s="334"/>
-      <c r="O1" s="334"/>
-      <c r="P1" s="334"/>
-      <c r="Q1" s="334"/>
-      <c r="R1" s="334"/>
-      <c r="S1" s="334"/>
-      <c r="T1" s="334"/>
-      <c r="U1" s="334"/>
-      <c r="V1" s="334"/>
-      <c r="W1" s="334"/>
-      <c r="X1" s="334"/>
-      <c r="Y1" s="334"/>
-      <c r="Z1" s="334"/>
-      <c r="AA1" s="334"/>
-      <c r="AB1" s="334"/>
-      <c r="AC1" s="334"/>
+      <c r="A1" s="337" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="337"/>
+      <c r="C1" s="337"/>
+      <c r="D1" s="337"/>
+      <c r="E1" s="337"/>
+      <c r="F1" s="337"/>
+      <c r="G1" s="337"/>
+      <c r="H1" s="337"/>
+      <c r="I1" s="337"/>
+      <c r="J1" s="337"/>
+      <c r="K1" s="337"/>
+      <c r="L1" s="337"/>
+      <c r="M1" s="337"/>
+      <c r="N1" s="337"/>
+      <c r="O1" s="337"/>
+      <c r="P1" s="337"/>
+      <c r="Q1" s="337"/>
+      <c r="R1" s="337"/>
+      <c r="S1" s="337"/>
+      <c r="T1" s="337"/>
+      <c r="U1" s="337"/>
+      <c r="V1" s="337"/>
+      <c r="W1" s="337"/>
+      <c r="X1" s="337"/>
+      <c r="Y1" s="337"/>
+      <c r="Z1" s="337"/>
+      <c r="AA1" s="337"/>
+      <c r="AB1" s="337"/>
+      <c r="AC1" s="337"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -8206,37 +8206,37 @@
       <c r="AC40" s="213"/>
     </row>
     <row r="41" spans="1:29" ht="18" x14ac:dyDescent="0.25">
-      <c r="A41" s="334" t="s">
+      <c r="A41" s="337" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="334"/>
-      <c r="C41" s="334"/>
-      <c r="D41" s="334"/>
-      <c r="E41" s="334"/>
-      <c r="F41" s="334"/>
-      <c r="G41" s="334"/>
-      <c r="H41" s="334"/>
-      <c r="I41" s="334"/>
-      <c r="J41" s="334"/>
-      <c r="K41" s="334"/>
-      <c r="L41" s="334"/>
-      <c r="M41" s="334"/>
-      <c r="N41" s="334"/>
-      <c r="O41" s="334"/>
-      <c r="P41" s="334"/>
-      <c r="Q41" s="334"/>
-      <c r="R41" s="334"/>
-      <c r="S41" s="334"/>
-      <c r="T41" s="334"/>
-      <c r="U41" s="334"/>
-      <c r="V41" s="334"/>
-      <c r="W41" s="334"/>
-      <c r="X41" s="334"/>
-      <c r="Y41" s="334"/>
-      <c r="Z41" s="334"/>
-      <c r="AA41" s="334"/>
-      <c r="AB41" s="334"/>
-      <c r="AC41" s="334"/>
+      <c r="B41" s="337"/>
+      <c r="C41" s="337"/>
+      <c r="D41" s="337"/>
+      <c r="E41" s="337"/>
+      <c r="F41" s="337"/>
+      <c r="G41" s="337"/>
+      <c r="H41" s="337"/>
+      <c r="I41" s="337"/>
+      <c r="J41" s="337"/>
+      <c r="K41" s="337"/>
+      <c r="L41" s="337"/>
+      <c r="M41" s="337"/>
+      <c r="N41" s="337"/>
+      <c r="O41" s="337"/>
+      <c r="P41" s="337"/>
+      <c r="Q41" s="337"/>
+      <c r="R41" s="337"/>
+      <c r="S41" s="337"/>
+      <c r="T41" s="337"/>
+      <c r="U41" s="337"/>
+      <c r="V41" s="337"/>
+      <c r="W41" s="337"/>
+      <c r="X41" s="337"/>
+      <c r="Y41" s="337"/>
+      <c r="Z41" s="337"/>
+      <c r="AA41" s="337"/>
+      <c r="AB41" s="337"/>
+      <c r="AC41" s="337"/>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="9"/>
@@ -12865,14 +12865,14 @@
     </row>
     <row r="2" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="353" t="s">
+      <c r="B2" s="351" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="353"/>
-      <c r="D2" s="354" t="s">
+      <c r="C2" s="351"/>
+      <c r="D2" s="352" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="354"/>
+      <c r="E2" s="352"/>
       <c r="F2" s="233" t="s">
         <v>163</v>
       </c>
@@ -12950,59 +12950,59 @@
     </row>
     <row r="3" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="353" t="s">
+      <c r="B3" s="351" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="353"/>
-      <c r="D3" s="354" t="s">
+      <c r="C3" s="351"/>
+      <c r="D3" s="352" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="354"/>
-      <c r="F3" s="349" t="s">
+      <c r="E3" s="352"/>
+      <c r="F3" s="345" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="349" t="s">
+      <c r="G3" s="345" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="349" t="s">
+      <c r="H3" s="345" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="349" t="s">
+      <c r="I3" s="345" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="349" t="s">
+      <c r="J3" s="345" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="349" t="s">
+      <c r="K3" s="345" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="349" t="s">
+      <c r="L3" s="345" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="349" t="s">
+      <c r="M3" s="345" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="340" t="s">
+      <c r="N3" s="350" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="340" t="s">
+      <c r="O3" s="350" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="339"/>
-      <c r="Q3" s="341" t="s">
+      <c r="P3" s="357"/>
+      <c r="Q3" s="358" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="342"/>
-      <c r="S3" s="343"/>
-      <c r="T3" s="344" t="s">
+      <c r="R3" s="359"/>
+      <c r="S3" s="360"/>
+      <c r="T3" s="361" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="345"/>
-      <c r="V3" s="346"/>
-      <c r="W3" s="337" t="s">
+      <c r="U3" s="362"/>
+      <c r="V3" s="363"/>
+      <c r="W3" s="355" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="337" t="s">
+      <c r="X3" s="355" t="s">
         <v>162</v>
       </c>
     </row>
@@ -13020,17 +13020,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="349"/>
-      <c r="G4" s="355"/>
-      <c r="H4" s="355"/>
-      <c r="I4" s="349"/>
-      <c r="J4" s="349"/>
-      <c r="K4" s="349"/>
-      <c r="L4" s="349"/>
-      <c r="M4" s="349"/>
-      <c r="N4" s="340"/>
-      <c r="O4" s="340"/>
-      <c r="P4" s="339"/>
+      <c r="F4" s="345"/>
+      <c r="G4" s="346"/>
+      <c r="H4" s="346"/>
+      <c r="I4" s="345"/>
+      <c r="J4" s="345"/>
+      <c r="K4" s="345"/>
+      <c r="L4" s="345"/>
+      <c r="M4" s="345"/>
+      <c r="N4" s="350"/>
+      <c r="O4" s="350"/>
+      <c r="P4" s="357"/>
       <c r="Q4" s="195" t="s">
         <v>140</v>
       </c>
@@ -13049,8 +13049,8 @@
       <c r="V4" s="237" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="338"/>
-      <c r="X4" s="338"/>
+      <c r="W4" s="356"/>
+      <c r="X4" s="356"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -13588,7 +13588,7 @@
       <c r="Z12" s="124"/>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="357" t="s">
+      <c r="A13" s="339" t="s">
         <v>178</v>
       </c>
       <c r="B13" s="296">
@@ -13656,7 +13656,7 @@
       <c r="Z13" s="124"/>
     </row>
     <row r="14" spans="1:32" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="357"/>
+      <c r="A14" s="339"/>
       <c r="B14" s="296">
         <v>33</v>
       </c>
@@ -13722,7 +13722,7 @@
       <c r="Z14" s="124"/>
     </row>
     <row r="15" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="357"/>
+      <c r="A15" s="339"/>
       <c r="B15" s="296">
         <v>32</v>
       </c>
@@ -13787,7 +13787,7 @@
       </c>
     </row>
     <row r="16" spans="1:32" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="357"/>
+      <c r="A16" s="339"/>
       <c r="B16" s="296">
         <v>0</v>
       </c>
@@ -13852,7 +13852,7 @@
       </c>
     </row>
     <row r="17" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="357"/>
+      <c r="A17" s="339"/>
       <c r="B17" s="296">
         <v>1</v>
       </c>
@@ -14056,7 +14056,7 @@
       </c>
     </row>
     <row r="20" spans="1:24" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="360" t="s">
+      <c r="A20" s="347" t="s">
         <v>180</v>
       </c>
       <c r="B20" s="296">
@@ -14123,7 +14123,7 @@
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="360"/>
+      <c r="A21" s="347"/>
       <c r="B21" s="296">
         <v>33</v>
       </c>
@@ -14188,7 +14188,7 @@
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="360"/>
+      <c r="A22" s="347"/>
       <c r="B22" s="296">
         <v>32</v>
       </c>
@@ -14253,7 +14253,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="360"/>
+      <c r="A23" s="347"/>
       <c r="B23" s="296">
         <v>0</v>
       </c>
@@ -14318,7 +14318,7 @@
       </c>
     </row>
     <row r="24" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="360"/>
+      <c r="A24" s="347"/>
       <c r="B24" s="296">
         <v>1</v>
       </c>
@@ -14522,7 +14522,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="357" t="s">
+      <c r="A27" s="339" t="s">
         <v>179</v>
       </c>
       <c r="B27" s="296">
@@ -14589,7 +14589,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="357"/>
+      <c r="A28" s="339"/>
       <c r="B28" s="296">
         <v>33</v>
       </c>
@@ -14654,7 +14654,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="357"/>
+      <c r="A29" s="339"/>
       <c r="B29" s="296">
         <v>32</v>
       </c>
@@ -14719,7 +14719,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="357"/>
+      <c r="A30" s="339"/>
       <c r="B30" s="296">
         <v>0</v>
       </c>
@@ -14783,7 +14783,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="357"/>
+      <c r="A31" s="339"/>
       <c r="B31" s="296">
         <v>1</v>
       </c>
@@ -19742,7 +19742,7 @@
       </c>
     </row>
     <row r="104" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="361" t="s">
+      <c r="A104" s="348" t="s">
         <v>181</v>
       </c>
       <c r="B104" s="219">
@@ -19797,13 +19797,13 @@
       <c r="R104" s="187"/>
       <c r="S104" s="187"/>
       <c r="T104" s="240">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U104" s="185"/>
       <c r="V104" s="230"/>
       <c r="W104" s="186">
         <f>J104-(T104*($M$2-$K$1)+(U104*($M$2-$M$1)))</f>
-        <v>2638.6</v>
+        <v>2656.33</v>
       </c>
       <c r="X104" s="183">
         <f>H104*$M$2</f>
@@ -19811,7 +19811,7 @@
       </c>
     </row>
     <row r="105" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="361"/>
+      <c r="A105" s="348"/>
       <c r="B105" s="219">
         <v>0</v>
       </c>
@@ -19876,7 +19876,7 @@
       </c>
     </row>
     <row r="106" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="361"/>
+      <c r="A106" s="348"/>
       <c r="B106" s="219">
         <v>0</v>
       </c>
@@ -19941,7 +19941,7 @@
       </c>
     </row>
     <row r="107" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="361"/>
+      <c r="A107" s="348"/>
       <c r="B107" s="219">
         <v>0</v>
       </c>
@@ -20006,7 +20006,7 @@
       </c>
     </row>
     <row r="108" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="361"/>
+      <c r="A108" s="348"/>
       <c r="B108" s="219">
         <v>0</v>
       </c>
@@ -20123,7 +20123,7 @@
       </c>
       <c r="O109" s="21">
         <f>(W109/N109)*100</f>
-        <v>98.528560830860528</v>
+        <v>98.857381305637972</v>
       </c>
       <c r="P109" s="193"/>
       <c r="Q109" s="182"/>
@@ -20134,7 +20134,7 @@
       <c r="V109" s="182"/>
       <c r="W109" s="194">
         <f>SUM(W103:W108)</f>
-        <v>5312.66</v>
+        <v>5330.3899999999994</v>
       </c>
       <c r="X109" s="194">
         <f>SUM(X103:X108)</f>
@@ -21143,7 +21143,7 @@
       </c>
     </row>
     <row r="125" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="362" t="s">
+      <c r="A125" s="349" t="s">
         <v>183</v>
       </c>
       <c r="B125" s="296">
@@ -21212,7 +21212,7 @@
       </c>
     </row>
     <row r="126" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="362"/>
+      <c r="A126" s="349"/>
       <c r="B126" s="296">
         <v>33</v>
       </c>
@@ -21277,7 +21277,7 @@
       </c>
     </row>
     <row r="127" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="362"/>
+      <c r="A127" s="349"/>
       <c r="B127" s="296">
         <v>32</v>
       </c>
@@ -21342,7 +21342,7 @@
       </c>
     </row>
     <row r="128" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="362"/>
+      <c r="A128" s="349"/>
       <c r="B128" s="296">
         <v>0</v>
       </c>
@@ -21407,7 +21407,7 @@
       </c>
     </row>
     <row r="129" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="362"/>
+      <c r="A129" s="349"/>
       <c r="B129" s="296">
         <v>1</v>
       </c>
@@ -21611,7 +21611,7 @@
       </c>
     </row>
     <row r="132" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="362" t="s">
+      <c r="A132" s="349" t="s">
         <v>182</v>
       </c>
       <c r="B132" s="296">
@@ -21680,7 +21680,7 @@
       </c>
     </row>
     <row r="133" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="362"/>
+      <c r="A133" s="349"/>
       <c r="B133" s="296">
         <v>33</v>
       </c>
@@ -21745,7 +21745,7 @@
       </c>
     </row>
     <row r="134" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="362"/>
+      <c r="A134" s="349"/>
       <c r="B134" s="296">
         <v>32</v>
       </c>
@@ -21810,7 +21810,7 @@
       </c>
     </row>
     <row r="135" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="362"/>
+      <c r="A135" s="349"/>
       <c r="B135" s="296">
         <v>0</v>
       </c>
@@ -21875,7 +21875,7 @@
       </c>
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="362"/>
+      <c r="A136" s="349"/>
       <c r="B136" s="296">
         <v>1</v>
       </c>
@@ -23074,7 +23074,7 @@
       <c r="Z153" s="124"/>
     </row>
     <row r="154" spans="1:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="362" t="s">
+      <c r="A154" s="349" t="s">
         <v>184</v>
       </c>
       <c r="B154" s="219">
@@ -23143,7 +23143,7 @@
       <c r="Z154" s="124"/>
     </row>
     <row r="155" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="362"/>
+      <c r="A155" s="349"/>
       <c r="B155" s="219">
         <v>0</v>
       </c>
@@ -23210,7 +23210,7 @@
       <c r="Z155" s="124"/>
     </row>
     <row r="156" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="362"/>
+      <c r="A156" s="349"/>
       <c r="B156" s="219">
         <v>0</v>
       </c>
@@ -23481,7 +23481,7 @@
       </c>
     </row>
     <row r="160" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="356" t="s">
+      <c r="A160" s="338" t="s">
         <v>185</v>
       </c>
       <c r="B160" s="296">
@@ -23551,7 +23551,7 @@
       <c r="Y160" s="172"/>
     </row>
     <row r="161" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="356"/>
+      <c r="A161" s="338"/>
       <c r="B161" s="296">
         <v>33</v>
       </c>
@@ -23616,7 +23616,7 @@
       </c>
     </row>
     <row r="162" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="356"/>
+      <c r="A162" s="338"/>
       <c r="B162" s="296">
         <v>32</v>
       </c>
@@ -23681,7 +23681,7 @@
       </c>
     </row>
     <row r="163" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="356"/>
+      <c r="A163" s="338"/>
       <c r="B163" s="296">
         <v>0</v>
       </c>
@@ -23746,7 +23746,7 @@
       </c>
     </row>
     <row r="164" spans="1:25" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="356"/>
+      <c r="A164" s="338"/>
       <c r="B164" s="296">
         <v>1</v>
       </c>
@@ -23811,7 +23811,7 @@
       </c>
     </row>
     <row r="165" spans="1:25" s="124" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="356"/>
+      <c r="A165" s="338"/>
       <c r="B165" s="296">
         <v>3</v>
       </c>
@@ -23876,7 +23876,7 @@
       </c>
     </row>
     <row r="166" spans="1:25" s="124" customFormat="1" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="356"/>
+      <c r="A166" s="338"/>
       <c r="B166" s="296">
         <v>2</v>
       </c>
@@ -24080,7 +24080,7 @@
       </c>
     </row>
     <row r="169" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="356" t="s">
+      <c r="A169" s="338" t="s">
         <v>185</v>
       </c>
       <c r="B169" s="296">
@@ -24150,7 +24150,7 @@
       <c r="Y169" s="172"/>
     </row>
     <row r="170" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="356"/>
+      <c r="A170" s="338"/>
       <c r="B170" s="296">
         <v>33</v>
       </c>
@@ -24215,7 +24215,7 @@
       </c>
     </row>
     <row r="171" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="356"/>
+      <c r="A171" s="338"/>
       <c r="B171" s="296">
         <v>32</v>
       </c>
@@ -24280,7 +24280,7 @@
       </c>
     </row>
     <row r="172" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="356"/>
+      <c r="A172" s="338"/>
       <c r="B172" s="296">
         <v>0</v>
       </c>
@@ -24345,7 +24345,7 @@
       </c>
     </row>
     <row r="173" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A173" s="356"/>
+      <c r="A173" s="338"/>
       <c r="B173" s="296">
         <v>1</v>
       </c>
@@ -24410,7 +24410,7 @@
       </c>
     </row>
     <row r="174" spans="1:25" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="356"/>
+      <c r="A174" s="338"/>
       <c r="B174" s="296">
         <v>3</v>
       </c>
@@ -24475,7 +24475,7 @@
       </c>
     </row>
     <row r="175" spans="1:25" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="356"/>
+      <c r="A175" s="338"/>
       <c r="B175" s="296">
         <v>2</v>
       </c>
@@ -24679,7 +24679,7 @@
       </c>
     </row>
     <row r="178" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="356" t="s">
+      <c r="A178" s="338" t="s">
         <v>185</v>
       </c>
       <c r="B178" s="296">
@@ -24749,7 +24749,7 @@
       <c r="Y178" s="172"/>
     </row>
     <row r="179" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A179" s="356"/>
+      <c r="A179" s="338"/>
       <c r="B179" s="296">
         <v>33</v>
       </c>
@@ -24814,7 +24814,7 @@
       </c>
     </row>
     <row r="180" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="356"/>
+      <c r="A180" s="338"/>
       <c r="B180" s="296">
         <v>32</v>
       </c>
@@ -24879,7 +24879,7 @@
       </c>
     </row>
     <row r="181" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="356"/>
+      <c r="A181" s="338"/>
       <c r="B181" s="296">
         <v>0</v>
       </c>
@@ -24944,7 +24944,7 @@
       </c>
     </row>
     <row r="182" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A182" s="356"/>
+      <c r="A182" s="338"/>
       <c r="B182" s="296">
         <v>1</v>
       </c>
@@ -25009,7 +25009,7 @@
       </c>
     </row>
     <row r="183" spans="1:30" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="356"/>
+      <c r="A183" s="338"/>
       <c r="B183" s="296">
         <v>3</v>
       </c>
@@ -25074,7 +25074,7 @@
       </c>
     </row>
     <row r="184" spans="1:30" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="356"/>
+      <c r="A184" s="338"/>
       <c r="B184" s="296">
         <v>2</v>
       </c>
@@ -25283,7 +25283,7 @@
       <c r="AD186" s="124"/>
     </row>
     <row r="187" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="356" t="s">
+      <c r="A187" s="338" t="s">
         <v>185</v>
       </c>
       <c r="B187" s="296">
@@ -25357,7 +25357,7 @@
       <c r="AD187" s="124"/>
     </row>
     <row r="188" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A188" s="356"/>
+      <c r="A188" s="338"/>
       <c r="B188" s="296">
         <v>33</v>
       </c>
@@ -25424,7 +25424,7 @@
       </c>
     </row>
     <row r="189" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="356"/>
+      <c r="A189" s="338"/>
       <c r="B189" s="296">
         <v>32</v>
       </c>
@@ -25489,7 +25489,7 @@
       </c>
     </row>
     <row r="190" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="356"/>
+      <c r="A190" s="338"/>
       <c r="B190" s="296">
         <v>0</v>
       </c>
@@ -25554,7 +25554,7 @@
       </c>
     </row>
     <row r="191" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="356"/>
+      <c r="A191" s="338"/>
       <c r="B191" s="296">
         <v>1</v>
       </c>
@@ -25619,7 +25619,7 @@
       </c>
     </row>
     <row r="192" spans="1:30" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="356"/>
+      <c r="A192" s="338"/>
       <c r="B192" s="296">
         <v>3</v>
       </c>
@@ -25684,7 +25684,7 @@
       </c>
     </row>
     <row r="193" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="356"/>
+      <c r="A193" s="338"/>
       <c r="B193" s="296">
         <v>2</v>
       </c>
@@ -25888,7 +25888,7 @@
       </c>
     </row>
     <row r="196" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="356" t="s">
+      <c r="A196" s="338" t="s">
         <v>185</v>
       </c>
       <c r="B196" s="296">
@@ -25957,7 +25957,7 @@
       </c>
     </row>
     <row r="197" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="356"/>
+      <c r="A197" s="338"/>
       <c r="B197" s="296">
         <v>33</v>
       </c>
@@ -26022,7 +26022,7 @@
       </c>
     </row>
     <row r="198" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="356"/>
+      <c r="A198" s="338"/>
       <c r="B198" s="296">
         <v>32</v>
       </c>
@@ -26087,7 +26087,7 @@
       </c>
     </row>
     <row r="199" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="356"/>
+      <c r="A199" s="338"/>
       <c r="B199" s="296">
         <v>0</v>
       </c>
@@ -26152,7 +26152,7 @@
       </c>
     </row>
     <row r="200" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="356"/>
+      <c r="A200" s="338"/>
       <c r="B200" s="296">
         <v>1</v>
       </c>
@@ -26217,7 +26217,7 @@
       </c>
     </row>
     <row r="201" spans="1:24" s="124" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="356"/>
+      <c r="A201" s="338"/>
       <c r="B201" s="296">
         <v>3</v>
       </c>
@@ -26282,7 +26282,7 @@
       </c>
     </row>
     <row r="202" spans="1:24" s="124" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="356"/>
+      <c r="A202" s="338"/>
       <c r="B202" s="296">
         <v>2</v>
       </c>
@@ -26486,7 +26486,7 @@
       </c>
     </row>
     <row r="205" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="356" t="s">
+      <c r="A205" s="338" t="s">
         <v>185</v>
       </c>
       <c r="B205" s="116">
@@ -26553,7 +26553,7 @@
       </c>
     </row>
     <row r="206" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="356"/>
+      <c r="A206" s="338"/>
       <c r="B206" s="116">
         <v>0</v>
       </c>
@@ -26620,7 +26620,7 @@
       </c>
     </row>
     <row r="207" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="356"/>
+      <c r="A207" s="338"/>
       <c r="B207" s="116">
         <v>0</v>
       </c>
@@ -26687,7 +26687,7 @@
       </c>
     </row>
     <row r="208" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="356"/>
+      <c r="A208" s="338"/>
       <c r="B208" s="116">
         <v>0</v>
       </c>
@@ -26752,7 +26752,7 @@
       </c>
     </row>
     <row r="209" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="356"/>
+      <c r="A209" s="338"/>
       <c r="B209" s="116">
         <v>0</v>
       </c>
@@ -26817,7 +26817,7 @@
       </c>
     </row>
     <row r="210" spans="1:25" s="124" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="356"/>
+      <c r="A210" s="338"/>
       <c r="B210" s="116">
         <v>3</v>
       </c>
@@ -26832,7 +26832,7 @@
         <f>'Data Ocupacion'!BG39</f>
         <v>1</v>
       </c>
-      <c r="F210" s="377" t="s">
+      <c r="F210" s="334" t="s">
         <v>152</v>
       </c>
       <c r="G210" s="329">
@@ -26882,7 +26882,7 @@
       </c>
     </row>
     <row r="211" spans="1:25" s="124" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="356"/>
+      <c r="A211" s="338"/>
       <c r="B211" s="116">
         <v>2</v>
       </c>
@@ -26897,7 +26897,7 @@
         <f>'Data Ocupacion'!BG40</f>
         <v>0</v>
       </c>
-      <c r="F211" s="377" t="s">
+      <c r="F211" s="334" t="s">
         <v>151</v>
       </c>
       <c r="G211" s="329">
@@ -26966,31 +26966,31 @@
       </c>
       <c r="F212" s="119"/>
       <c r="G212" s="119">
-        <f>SUM(G204:G211)</f>
+        <f t="shared" ref="G212:M212" si="201">SUM(G204:G211)</f>
         <v>156</v>
       </c>
       <c r="H212" s="119">
-        <f>SUM(H204:H211)</f>
+        <f t="shared" si="201"/>
         <v>157</v>
       </c>
       <c r="I212" s="119">
-        <f>SUM(I204:I211)</f>
+        <f t="shared" si="201"/>
         <v>153</v>
       </c>
       <c r="J212" s="119">
-        <f>SUM(J204:J211)</f>
+        <f t="shared" si="201"/>
         <v>6617.1200000000008</v>
       </c>
       <c r="K212" s="119">
-        <f>SUM(K204:K211)</f>
+        <f t="shared" si="201"/>
         <v>6496.0300000000007</v>
       </c>
       <c r="L212" s="119">
-        <f>SUM(L204:L211)</f>
+        <f t="shared" si="201"/>
         <v>688180.48</v>
       </c>
       <c r="M212" s="119">
-        <f>SUM(M204:M211)</f>
+        <f t="shared" si="201"/>
         <v>15912</v>
       </c>
       <c r="N212" s="123">
@@ -27576,38 +27576,38 @@
     <row r="234" spans="1:29" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="235" spans="1:29" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235"/>
-      <c r="B235" s="350" t="s">
+      <c r="B235" s="342" t="s">
         <v>56</v>
       </c>
-      <c r="C235" s="351"/>
-      <c r="D235" s="351"/>
-      <c r="E235" s="351"/>
-      <c r="F235" s="351"/>
-      <c r="G235" s="352"/>
+      <c r="C235" s="343"/>
+      <c r="D235" s="343"/>
+      <c r="E235" s="343"/>
+      <c r="F235" s="343"/>
+      <c r="G235" s="344"/>
       <c r="H235" s="291"/>
-      <c r="I235" s="350" t="s">
+      <c r="I235" s="342" t="s">
         <v>57</v>
       </c>
-      <c r="J235" s="351"/>
-      <c r="K235" s="351"/>
-      <c r="L235" s="351"/>
-      <c r="M235" s="351"/>
-      <c r="N235" s="352"/>
-      <c r="P235" s="347" t="s">
+      <c r="J235" s="343"/>
+      <c r="K235" s="343"/>
+      <c r="L235" s="343"/>
+      <c r="M235" s="343"/>
+      <c r="N235" s="344"/>
+      <c r="P235" s="364" t="s">
         <v>139</v>
       </c>
-      <c r="Q235" s="347"/>
-      <c r="R235" s="347"/>
-      <c r="S235" s="348"/>
-      <c r="T235" s="344" t="s">
+      <c r="Q235" s="364"/>
+      <c r="R235" s="364"/>
+      <c r="S235" s="365"/>
+      <c r="T235" s="361" t="s">
         <v>142</v>
       </c>
-      <c r="U235" s="345"/>
-      <c r="V235" s="346"/>
-      <c r="W235" s="335" t="s">
+      <c r="U235" s="362"/>
+      <c r="V235" s="363"/>
+      <c r="W235" s="353" t="s">
         <v>143</v>
       </c>
-      <c r="X235" s="335" t="s">
+      <c r="X235" s="353" t="s">
         <v>162</v>
       </c>
     </row>
@@ -27673,23 +27673,23 @@
       <c r="V236" s="228" t="s">
         <v>146</v>
       </c>
-      <c r="W236" s="336"/>
-      <c r="X236" s="336"/>
+      <c r="W236" s="354"/>
+      <c r="X236" s="354"/>
     </row>
     <row r="237" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B237" s="114">
-        <f>B5+B12+B19+B26+B33+B40+B47+B54+B61+B68+B75+B82+B89+B96+B103+B110+B117+B124+B131+B138+B145+B152+B159+B168+B177+B186+B195+B204+B213+B220+B227</f>
+        <f t="shared" ref="B237:C239" si="202">B5+B12+B19+B26+B33+B40+B47+B54+B61+B68+B75+B82+B89+B96+B103+B110+B117+B124+B131+B138+B145+B152+B159+B168+B177+B186+B195+B204+B213+B220+B227</f>
         <v>1969</v>
       </c>
       <c r="C237" s="114">
-        <f>C5+C12+C19+C26+C33+C40+C47+C54+C61+C68+C75+C82+C89+C96+C103+C110+C117+C124+C131+C138+C145+C152+C159+C168+C177+C186+C195+C204+C213+C220+C227</f>
+        <f t="shared" si="202"/>
         <v>115</v>
       </c>
       <c r="D237" s="114">
-        <f t="shared" ref="D237:D244" si="201">B237+C237</f>
+        <f t="shared" ref="D237:D244" si="203">B237+C237</f>
         <v>2084</v>
       </c>
       <c r="E237" s="139">
@@ -27701,20 +27701,20 @@
         <v>94842.87</v>
       </c>
       <c r="G237" s="139">
-        <f t="shared" ref="G237:G244" si="202">F237*104</f>
+        <f t="shared" ref="G237:G244" si="204">F237*104</f>
         <v>9863658.4800000004</v>
       </c>
       <c r="H237" s="139"/>
       <c r="I237" s="114">
-        <f>D5+D12+D26+D33+D40+D47+D54+D61+D68+D75+D82+D89+D96+D103+D110+D117+D124+D131+D138+D145+D152+D159+D168+D177+D186+D195+D204+D213+D220+D227+D19</f>
+        <f t="shared" ref="I237:J240" si="205">D5+D12+D26+D33+D40+D47+D54+D61+D68+D75+D82+D89+D96+D103+D110+D117+D124+D131+D138+D145+D152+D159+D168+D177+D186+D195+D204+D213+D220+D227+D19</f>
         <v>1967</v>
       </c>
       <c r="J237" s="114">
-        <f>E5+E12+E26+E33+E40+E47+E54+E61+E68+E75+E82+E89+E96+E103+E110+E117+E124+E131+E138+E145+E152+E159+E168+E177+E186+E195+E204+E213+E220+E227+E19</f>
+        <f t="shared" si="205"/>
         <v>119</v>
       </c>
       <c r="K237" s="114">
-        <f t="shared" ref="K237:K242" si="203">I237+J237</f>
+        <f t="shared" ref="K237:K242" si="206">I237+J237</f>
         <v>2086</v>
       </c>
       <c r="L237" s="139">
@@ -27726,7 +27726,7 @@
         <v>95101.650000000009</v>
       </c>
       <c r="N237" s="139">
-        <f t="shared" ref="N237:N242" si="204">M237*104</f>
+        <f t="shared" ref="N237:N242" si="207">M237*104</f>
         <v>9890571.6000000015</v>
       </c>
       <c r="O237" s="124"/>
@@ -27748,7 +27748,7 @@
       </c>
       <c r="T237" s="210">
         <f>SUM(T204,T195,T186,T177,T168,T159,T152,T145,T138,T131,T124,T117,T110,T103,T96,T89,T82,T75,T68,T61,T54,T47,T40,T33,T26,T19,T12,T5,T213,T220,T227)+T6+T13+T20+T27+T34+T41+T48+T55+T62+T69+T76+T83+T90+T97+T104+T111+T118+T125+T132+T139+T146+T153+T160+T169+T178+T187+T196+T205+T214+T221+T228</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U237" s="210">
         <f>SUM(U204,U195,U186,U177,U168,U159,U152,U145,U138,U131,U124,U117,U110,U103,U96,U89,U82,U75,U68,U61,U54,U47,U40,U33,U26,U19,U12,U5,U213,U220,U228)</f>
@@ -27760,7 +27760,7 @@
       </c>
       <c r="W237" s="232">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W167+W176+W185+W194+W203+W212+W219+W226+W233</f>
-        <v>228609.59999999998</v>
+        <v>228627.33</v>
       </c>
       <c r="X237" s="232">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X167+X176+X185+X194+X203+X212+X219+X226+X233</f>
@@ -27772,15 +27772,15 @@
         <v>52</v>
       </c>
       <c r="B238" s="114">
-        <f>B6+B13+B20+B27+B34+B41+B48+B55+B62+B69+B76+B83+B90+B97+B104+B111+B118+B125+B132+B139+B146+B153+B160+B169+B178+B187+B196+B205+B214+B221+B228</f>
+        <f t="shared" si="202"/>
         <v>1979</v>
       </c>
       <c r="C238" s="114">
-        <f>C6+C13+C20+C27+C34+C41+C48+C55+C62+C69+C76+C83+C90+C97+C104+C111+C118+C125+C132+C139+C146+C153+C160+C169+C178+C187+C196+C205+C214+C221+C228</f>
+        <f t="shared" si="202"/>
         <v>109</v>
       </c>
       <c r="D238" s="114">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>2088</v>
       </c>
       <c r="E238" s="139">
@@ -27792,24 +27792,24 @@
         <v>94756.61</v>
       </c>
       <c r="G238" s="139">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>9854687.4399999995</v>
       </c>
       <c r="H238" s="139"/>
       <c r="I238" s="114">
-        <f>D6+D13+D27+D34+D41+D48+D55+D62+D69+D76+D83+D90+D97+D104+D111+D118+D125+D132+D139+D146+D153+D160+D169+D178+D187+D196+D205+D214+D221+D228+D20</f>
+        <f t="shared" si="205"/>
         <v>1976</v>
       </c>
       <c r="J238" s="114">
-        <f>E6+E13+E27+E34+E41+E48+E55+E62+E69+E76+E83+E90+E97+E104+E111+E118+E125+E132+E139+E146+E153+E160+E169+E178+E187+E196+E205+E214+E221+E228+E20</f>
+        <f t="shared" si="205"/>
         <v>112</v>
       </c>
       <c r="K238" s="114">
-        <f t="shared" si="203"/>
+        <f t="shared" si="206"/>
         <v>2088</v>
       </c>
       <c r="L238" s="139">
-        <f t="shared" ref="L238" si="205">K238*43.13</f>
+        <f t="shared" ref="L238" si="208">K238*43.13</f>
         <v>90055.44</v>
       </c>
       <c r="M238" s="139">
@@ -27817,7 +27817,7 @@
         <v>94886</v>
       </c>
       <c r="N238" s="139">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>9868144</v>
       </c>
       <c r="O238" s="124"/>
@@ -27829,15 +27829,15 @@
         <v>36</v>
       </c>
       <c r="B239" s="114">
-        <f>B7+B14+B21+B28+B35+B42+B49+B56+B63+B70+B77+B84+B91+B98+B105+B112+B119+B126+B133+B140+B147+B154+B161+B170+B179+B188+B197+B206+B215+B222+B229</f>
+        <f t="shared" si="202"/>
         <v>660</v>
       </c>
       <c r="C239" s="114">
-        <f>C7+C14+C21+C28+C35+C42+C49+C56+C63+C70+C77+C84+C91+C98+C105+C112+C119+C126+C133+C140+C147+C154+C161+C170+C179+C188+C197+C206+C215+C222+C229</f>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
       <c r="D239" s="114">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>660</v>
       </c>
       <c r="E239" s="139">
@@ -27849,20 +27849,20 @@
         <v>19212.599999999999</v>
       </c>
       <c r="G239" s="139">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>1998110.4</v>
       </c>
       <c r="H239" s="139"/>
       <c r="I239" s="114">
-        <f>D7+D14+D28+D35+D42+D49+D56+D63+D70+D77+D84+D91+D98+D105+D112+D119+D126+D133+D140+D147+D154+D161+D170+D179+D188+D197+D206+D215+D222+D229+D21</f>
+        <f t="shared" si="205"/>
         <v>652</v>
       </c>
       <c r="J239" s="114">
-        <f>E7+E14+E28+E35+E42+E49+E56+E63+E70+E77+E84+E91+E98+E105+E112+E119+E126+E133+E140+E147+E154+E161+E170+E179+E188+E197+E206+E215+E222+E229+E21</f>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="K239" s="114">
-        <f t="shared" si="203"/>
+        <f t="shared" si="206"/>
         <v>652</v>
       </c>
       <c r="L239" s="139">
@@ -27874,7 +27874,7 @@
         <v>18979.72</v>
       </c>
       <c r="N239" s="139">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>1973890.8800000001</v>
       </c>
       <c r="O239" s="124"/>
@@ -27893,7 +27893,7 @@
         <v>0</v>
       </c>
       <c r="D240" s="114">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>640</v>
       </c>
       <c r="E240" s="139">
@@ -27905,20 +27905,20 @@
         <v>18630.400000000001</v>
       </c>
       <c r="G240" s="139">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>1937561.6000000001</v>
       </c>
       <c r="H240" s="139"/>
       <c r="I240" s="114">
-        <f>D8+D15+D29+D36+D43+D50+D57+D64+D71+D78+D85+D92+D99+D106+D113+D120+D127+D134+D141+D148+D155+D162+D171+D180+D189+D198+D207+D216+D223+D230+D22</f>
+        <f t="shared" si="205"/>
         <v>634</v>
       </c>
       <c r="J240" s="114">
-        <f>E8+E15+E29+E36+E43+E50+E57+E64+E71+E78+E85+E92+E99+E106+E113+E120+E127+E134+E141+E148+E155+E162+E171+E180+E189+E198+E207+E216+E223+E230+E22</f>
+        <f t="shared" si="205"/>
         <v>1</v>
       </c>
       <c r="K240" s="114">
-        <f t="shared" si="203"/>
+        <f t="shared" si="206"/>
         <v>635</v>
       </c>
       <c r="L240" s="139">
@@ -27930,7 +27930,7 @@
         <v>18513.96</v>
       </c>
       <c r="N240" s="139">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>1925451.8399999999</v>
       </c>
       <c r="O240" s="124"/>
@@ -27952,7 +27952,7 @@
         <v>0</v>
       </c>
       <c r="D241" s="114">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>0</v>
       </c>
       <c r="E241" s="139">
@@ -27964,7 +27964,7 @@
         <v>0</v>
       </c>
       <c r="G241" s="139">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="H241" s="139"/>
@@ -27977,7 +27977,7 @@
         <v>0</v>
       </c>
       <c r="K241" s="114">
-        <f t="shared" si="203"/>
+        <f t="shared" si="206"/>
         <v>0</v>
       </c>
       <c r="L241" s="139">
@@ -27989,7 +27989,7 @@
         <v>0</v>
       </c>
       <c r="N241" s="139">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0</v>
       </c>
       <c r="O241" s="124"/>
@@ -28008,7 +28008,7 @@
         <v>0</v>
       </c>
       <c r="D242" s="114">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>20</v>
       </c>
       <c r="E242" s="139">
@@ -28020,7 +28020,7 @@
         <v>508</v>
       </c>
       <c r="G242" s="139">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>52832</v>
       </c>
       <c r="H242" s="139"/>
@@ -28033,7 +28033,7 @@
         <v>0</v>
       </c>
       <c r="K242" s="114">
-        <f t="shared" si="203"/>
+        <f t="shared" si="206"/>
         <v>21</v>
       </c>
       <c r="L242" s="139">
@@ -28045,7 +28045,7 @@
         <v>533.4</v>
       </c>
       <c r="N242" s="139">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>55473.599999999999</v>
       </c>
       <c r="O242" s="124"/>
@@ -28072,7 +28072,7 @@
         <v>6</v>
       </c>
       <c r="D243" s="114">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>24</v>
       </c>
       <c r="E243" s="139">
@@ -28084,7 +28084,7 @@
         <v>1044.8999999999999</v>
       </c>
       <c r="G243" s="139">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>108669.59999999999</v>
       </c>
       <c r="H243" s="139"/>
@@ -28097,7 +28097,7 @@
         <v>6</v>
       </c>
       <c r="K243" s="114">
-        <f t="shared" ref="K243:K244" si="206">I243+J243</f>
+        <f t="shared" ref="K243:K244" si="209">I243+J243</f>
         <v>24</v>
       </c>
       <c r="L243" s="139">
@@ -28109,7 +28109,7 @@
         <v>1044.8999999999999</v>
       </c>
       <c r="N243" s="139">
-        <f t="shared" ref="N243:N244" si="207">M243*104</f>
+        <f t="shared" ref="N243:N244" si="210">M243*104</f>
         <v>108669.59999999999</v>
       </c>
       <c r="AA243" s="101"/>
@@ -28129,7 +28129,7 @@
         <v>0</v>
       </c>
       <c r="D244" s="114">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>12</v>
       </c>
       <c r="E244" s="139">
@@ -28141,7 +28141,7 @@
         <v>99.600000000000009</v>
       </c>
       <c r="G244" s="139">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>10358.400000000001</v>
       </c>
       <c r="H244" s="139"/>
@@ -28154,7 +28154,7 @@
         <v>0</v>
       </c>
       <c r="K244" s="114">
-        <f t="shared" si="206"/>
+        <f t="shared" si="209"/>
         <v>12</v>
       </c>
       <c r="L244" s="139">
@@ -28166,7 +28166,7 @@
         <v>99.600000000000009</v>
       </c>
       <c r="N244" s="139">
-        <f t="shared" si="207"/>
+        <f t="shared" si="210"/>
         <v>10358.400000000001</v>
       </c>
       <c r="AA244" s="101"/>
@@ -28298,10 +28298,10 @@
     </row>
     <row r="249" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A249" s="24"/>
-      <c r="B249" s="358" t="s">
+      <c r="B249" s="340" t="s">
         <v>55</v>
       </c>
-      <c r="C249" s="359"/>
+      <c r="C249" s="341"/>
       <c r="D249" s="25" t="s">
         <v>65</v>
       </c>
@@ -28477,23 +28477,16 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="39">
-    <mergeCell ref="A205:A211"/>
-    <mergeCell ref="A196:A202"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B249:C249"/>
-    <mergeCell ref="B235:G235"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A104:A108"/>
-    <mergeCell ref="A125:A129"/>
-    <mergeCell ref="A132:A136"/>
-    <mergeCell ref="A154:A156"/>
-    <mergeCell ref="A160:A166"/>
-    <mergeCell ref="A169:A175"/>
-    <mergeCell ref="A178:A184"/>
-    <mergeCell ref="A187:A193"/>
+    <mergeCell ref="X235:X236"/>
+    <mergeCell ref="W235:W236"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="T235:V235"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="P235:S235"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="I235:N235"/>
@@ -28506,16 +28499,23 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="X235:X236"/>
-    <mergeCell ref="W235:W236"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="T235:V235"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="P235:S235"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A104:A108"/>
+    <mergeCell ref="A205:A211"/>
+    <mergeCell ref="A196:A202"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B249:C249"/>
+    <mergeCell ref="B235:G235"/>
+    <mergeCell ref="A125:A129"/>
+    <mergeCell ref="A132:A136"/>
+    <mergeCell ref="A154:A156"/>
+    <mergeCell ref="A160:A166"/>
+    <mergeCell ref="A169:A175"/>
+    <mergeCell ref="A178:A184"/>
+    <mergeCell ref="A187:A193"/>
   </mergeCells>
   <conditionalFormatting sqref="D33:E38 D204:E211">
     <cfRule type="expression" dxfId="47" priority="120">
@@ -28779,118 +28779,118 @@
   <sheetData>
     <row r="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
-      <c r="D1" s="363">
+      <c r="D1" s="366">
         <v>46054</v>
       </c>
-      <c r="E1" s="363"/>
-      <c r="F1" s="363">
+      <c r="E1" s="366"/>
+      <c r="F1" s="366">
         <v>46055</v>
       </c>
-      <c r="G1" s="363"/>
-      <c r="H1" s="363">
+      <c r="G1" s="366"/>
+      <c r="H1" s="366">
         <v>46056</v>
       </c>
-      <c r="I1" s="363"/>
-      <c r="J1" s="363">
+      <c r="I1" s="366"/>
+      <c r="J1" s="366">
         <v>46057</v>
       </c>
-      <c r="K1" s="363"/>
-      <c r="L1" s="363">
+      <c r="K1" s="366"/>
+      <c r="L1" s="366">
         <v>46058</v>
       </c>
-      <c r="M1" s="363"/>
-      <c r="N1" s="363">
+      <c r="M1" s="366"/>
+      <c r="N1" s="366">
         <v>46059</v>
       </c>
-      <c r="O1" s="363"/>
-      <c r="P1" s="363">
+      <c r="O1" s="366"/>
+      <c r="P1" s="366">
         <v>46060</v>
       </c>
-      <c r="Q1" s="363"/>
-      <c r="R1" s="363">
+      <c r="Q1" s="366"/>
+      <c r="R1" s="366">
         <v>46061</v>
       </c>
-      <c r="S1" s="363"/>
-      <c r="T1" s="363">
+      <c r="S1" s="366"/>
+      <c r="T1" s="366">
         <v>46062</v>
       </c>
-      <c r="U1" s="363"/>
-      <c r="V1" s="363">
+      <c r="U1" s="366"/>
+      <c r="V1" s="366">
         <v>46063</v>
       </c>
-      <c r="W1" s="363"/>
-      <c r="X1" s="363">
+      <c r="W1" s="366"/>
+      <c r="X1" s="366">
         <v>46064</v>
       </c>
-      <c r="Y1" s="363"/>
-      <c r="Z1" s="363">
+      <c r="Y1" s="366"/>
+      <c r="Z1" s="366">
         <v>46065</v>
       </c>
-      <c r="AA1" s="363"/>
-      <c r="AB1" s="363">
+      <c r="AA1" s="366"/>
+      <c r="AB1" s="366">
         <v>46066</v>
       </c>
-      <c r="AC1" s="363"/>
-      <c r="AD1" s="363">
+      <c r="AC1" s="366"/>
+      <c r="AD1" s="366">
         <v>46067</v>
       </c>
-      <c r="AE1" s="363"/>
-      <c r="AF1" s="363">
+      <c r="AE1" s="366"/>
+      <c r="AF1" s="366">
         <v>46068</v>
       </c>
-      <c r="AG1" s="363"/>
-      <c r="AH1" s="363">
+      <c r="AG1" s="366"/>
+      <c r="AH1" s="366">
         <v>46069</v>
       </c>
-      <c r="AI1" s="363"/>
-      <c r="AJ1" s="363">
+      <c r="AI1" s="366"/>
+      <c r="AJ1" s="366">
         <v>46070</v>
       </c>
-      <c r="AK1" s="363"/>
-      <c r="AL1" s="363">
+      <c r="AK1" s="366"/>
+      <c r="AL1" s="366">
         <v>46071</v>
       </c>
-      <c r="AM1" s="363"/>
-      <c r="AN1" s="363">
+      <c r="AM1" s="366"/>
+      <c r="AN1" s="366">
         <v>46072</v>
       </c>
-      <c r="AO1" s="363"/>
-      <c r="AP1" s="363">
+      <c r="AO1" s="366"/>
+      <c r="AP1" s="366">
         <v>46073</v>
       </c>
-      <c r="AQ1" s="363"/>
-      <c r="AR1" s="363">
+      <c r="AQ1" s="366"/>
+      <c r="AR1" s="366">
         <v>46074</v>
       </c>
-      <c r="AS1" s="363"/>
-      <c r="AT1" s="363">
+      <c r="AS1" s="366"/>
+      <c r="AT1" s="366">
         <v>46075</v>
       </c>
-      <c r="AU1" s="363"/>
-      <c r="AV1" s="363">
+      <c r="AU1" s="366"/>
+      <c r="AV1" s="366">
         <v>46076</v>
       </c>
-      <c r="AW1" s="363"/>
-      <c r="AX1" s="363">
+      <c r="AW1" s="366"/>
+      <c r="AX1" s="366">
         <v>46077</v>
       </c>
-      <c r="AY1" s="363"/>
-      <c r="AZ1" s="363">
+      <c r="AY1" s="366"/>
+      <c r="AZ1" s="366">
         <v>46078</v>
       </c>
-      <c r="BA1" s="363"/>
-      <c r="BB1" s="363">
+      <c r="BA1" s="366"/>
+      <c r="BB1" s="366">
         <v>46079</v>
       </c>
-      <c r="BC1" s="363"/>
-      <c r="BD1" s="363">
+      <c r="BC1" s="366"/>
+      <c r="BD1" s="366">
         <v>46080</v>
       </c>
-      <c r="BE1" s="363"/>
-      <c r="BF1" s="363">
+      <c r="BE1" s="366"/>
+      <c r="BF1" s="366">
         <v>46081</v>
       </c>
-      <c r="BG1" s="363"/>
+      <c r="BG1" s="366"/>
     </row>
     <row r="2" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
@@ -34638,10 +34638,10 @@
       </c>
     </row>
     <row r="41" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="A41" s="364" t="s">
+      <c r="A41" s="367" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="364"/>
+      <c r="B41" s="367"/>
       <c r="C41" s="8"/>
       <c r="D41" s="149">
         <f>SUM(D33:D38)</f>
@@ -37059,48 +37059,48 @@
       <c r="BE63" s="326"/>
     </row>
     <row r="64" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AD64" s="378"/>
-      <c r="AE64" s="378"/>
-      <c r="AF64" s="378"/>
-      <c r="AG64" s="378"/>
-      <c r="AH64" s="378"/>
-      <c r="AI64" s="378"/>
-      <c r="AJ64" s="379"/>
-      <c r="AK64" s="379"/>
-      <c r="AL64" s="379"/>
-      <c r="AM64" s="379"/>
-      <c r="AN64" s="379"/>
-      <c r="AO64" s="379"/>
-      <c r="AP64" s="379"/>
-      <c r="AQ64" s="379"/>
-      <c r="AR64" s="378"/>
-      <c r="AS64" s="378"/>
-      <c r="AT64" s="378"/>
-      <c r="AU64" s="378"/>
-      <c r="AV64" s="378"/>
-      <c r="AW64" s="378"/>
+      <c r="AD64" s="335"/>
+      <c r="AE64" s="335"/>
+      <c r="AF64" s="335"/>
+      <c r="AG64" s="335"/>
+      <c r="AH64" s="335"/>
+      <c r="AI64" s="335"/>
+      <c r="AJ64" s="336"/>
+      <c r="AK64" s="336"/>
+      <c r="AL64" s="336"/>
+      <c r="AM64" s="336"/>
+      <c r="AN64" s="336"/>
+      <c r="AO64" s="336"/>
+      <c r="AP64" s="336"/>
+      <c r="AQ64" s="336"/>
+      <c r="AR64" s="335"/>
+      <c r="AS64" s="335"/>
+      <c r="AT64" s="335"/>
+      <c r="AU64" s="335"/>
+      <c r="AV64" s="335"/>
+      <c r="AW64" s="335"/>
     </row>
     <row r="65" spans="29:69" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AD65" s="378"/>
-      <c r="AE65" s="378"/>
-      <c r="AF65" s="378"/>
-      <c r="AG65" s="378"/>
-      <c r="AH65" s="378"/>
-      <c r="AI65" s="378"/>
-      <c r="AJ65" s="379"/>
-      <c r="AK65" s="379"/>
-      <c r="AL65" s="379"/>
-      <c r="AM65" s="379"/>
-      <c r="AN65" s="379"/>
-      <c r="AO65" s="379"/>
-      <c r="AP65" s="379"/>
-      <c r="AQ65" s="379"/>
-      <c r="AR65" s="378"/>
-      <c r="AS65" s="378"/>
-      <c r="AT65" s="378"/>
-      <c r="AU65" s="378"/>
-      <c r="AV65" s="378"/>
-      <c r="AW65" s="378"/>
+      <c r="AD65" s="335"/>
+      <c r="AE65" s="335"/>
+      <c r="AF65" s="335"/>
+      <c r="AG65" s="335"/>
+      <c r="AH65" s="335"/>
+      <c r="AI65" s="335"/>
+      <c r="AJ65" s="336"/>
+      <c r="AK65" s="336"/>
+      <c r="AL65" s="336"/>
+      <c r="AM65" s="336"/>
+      <c r="AN65" s="336"/>
+      <c r="AO65" s="336"/>
+      <c r="AP65" s="336"/>
+      <c r="AQ65" s="336"/>
+      <c r="AR65" s="335"/>
+      <c r="AS65" s="335"/>
+      <c r="AT65" s="335"/>
+      <c r="AU65" s="335"/>
+      <c r="AV65" s="335"/>
+      <c r="AW65" s="335"/>
     </row>
     <row r="66" spans="29:69" x14ac:dyDescent="0.25">
       <c r="AN66" s="256"/>
@@ -37574,19 +37574,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="BF1:BG1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AN1:AO1"/>
@@ -37597,12 +37590,19 @@
     <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -39620,7 +39620,7 @@
       </c>
       <c r="Q24" s="83">
         <f>'KM-Servicio'!T104</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24" s="83">
         <f>'KM-Servicio'!T111</f>
@@ -40280,7 +40280,7 @@
       </c>
       <c r="B33" s="227">
         <f t="shared" si="0"/>
-        <v>228609.6</v>
+        <v>228627.33</v>
       </c>
       <c r="C33" s="91">
         <f>(C14*$B$14+C15*$B$15+C16*$B$16+C17*$B$17+C19*$B$19+C24*$B$24+C18*$B$18+C23*$B$23+C26*$B$26+C27*$B$27+C25*B25)</f>
@@ -40340,7 +40340,7 @@
       </c>
       <c r="Q33" s="91">
         <f>(Q14*$B$14+Q15*$B$15+Q16*$B$16+Q17*$B$17+Q19*$B$19+Q20*B20+Q24*$B$24+Q18*$B$18+Q23*$B$23+Q25*$B$25+Q26*$B$26)</f>
-        <v>5312.66</v>
+        <v>5330.39</v>
       </c>
       <c r="R33" s="91">
         <f>(R14*$B$14+R15*$B$15+R16*$B$16+R17*$B$17+R19*$B$19+R24*$B$24+R18*$B$18+R23*$B$23+R25*$B$25+R26*$B$26)</f>
@@ -40522,7 +40522,7 @@
       </c>
       <c r="B35" s="227">
         <f t="shared" si="0"/>
-        <v>23775398.399999999</v>
+        <v>23777242.319999997</v>
       </c>
       <c r="C35" s="91">
         <f t="shared" ref="C35:AD35" si="8">C33*104</f>
@@ -40582,7 +40582,7 @@
       </c>
       <c r="Q35" s="91">
         <f t="shared" si="8"/>
-        <v>552516.64</v>
+        <v>554360.56000000006</v>
       </c>
       <c r="R35" s="91">
         <f t="shared" si="8"/>
@@ -40643,7 +40643,7 @@
       </c>
       <c r="B36" s="89">
         <f t="shared" si="0"/>
-        <v>457219.2</v>
+        <v>457254.66</v>
       </c>
       <c r="C36" s="91">
         <f>C33*2</f>
@@ -40703,7 +40703,7 @@
       </c>
       <c r="Q36" s="91">
         <f t="shared" si="9"/>
-        <v>10625.32</v>
+        <v>10660.78</v>
       </c>
       <c r="R36" s="91">
         <f t="shared" si="9"/>
@@ -40885,7 +40885,7 @@
       </c>
       <c r="B38" s="227">
         <f t="shared" si="0"/>
-        <v>18128741.280000001</v>
+        <v>18130147.269000001</v>
       </c>
       <c r="C38" s="91">
         <f>C33*79.3</f>
@@ -40945,7 +40945,7 @@
       </c>
       <c r="Q38" s="91">
         <f t="shared" si="11"/>
-        <v>421293.93799999997</v>
+        <v>422699.92700000003</v>
       </c>
       <c r="R38" s="91">
         <f t="shared" si="11"/>
@@ -41311,19 +41311,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="365" t="s">
+      <c r="A2" s="368" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="366"/>
-      <c r="C2" s="366"/>
-      <c r="D2" s="366"/>
-      <c r="E2" s="366"/>
-      <c r="F2" s="366"/>
-      <c r="G2" s="366"/>
-      <c r="H2" s="366"/>
-      <c r="I2" s="366"/>
-      <c r="J2" s="366"/>
-      <c r="K2" s="366"/>
+      <c r="B2" s="369"/>
+      <c r="C2" s="369"/>
+      <c r="D2" s="369"/>
+      <c r="E2" s="369"/>
+      <c r="F2" s="369"/>
+      <c r="G2" s="369"/>
+      <c r="H2" s="369"/>
+      <c r="I2" s="369"/>
+      <c r="J2" s="369"/>
+      <c r="K2" s="369"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="158" t="s">
@@ -41962,15 +41962,15 @@
       </c>
       <c r="D18" s="12">
         <f>'KM-Servicio'!W109</f>
-        <v>5312.66</v>
+        <v>5330.3899999999994</v>
       </c>
       <c r="E18" s="12">
         <f t="shared" si="1"/>
-        <v>116915.18000000002</v>
+        <v>116932.91000000002</v>
       </c>
       <c r="F18" s="166">
         <f>'KM-Servicio'!O109</f>
-        <v>98.528560830860528</v>
+        <v>98.857381305637972</v>
       </c>
       <c r="G18" s="167">
         <f>SUM('KM-Servicio'!B109:C109)</f>
@@ -41982,7 +41982,7 @@
       </c>
       <c r="I18" s="12">
         <f>'Oferta Diaria'!Q38</f>
-        <v>421293.93799999997</v>
+        <v>422699.92700000003</v>
       </c>
       <c r="J18" s="319" t="s">
         <v>136</v>
@@ -42008,7 +42008,7 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="1"/>
-        <v>125733.53000000003</v>
+        <v>125751.26000000002</v>
       </c>
       <c r="F19" s="166">
         <f>'KM-Servicio'!O116</f>
@@ -42049,7 +42049,7 @@
       </c>
       <c r="E20" s="12">
         <f t="shared" si="1"/>
-        <v>134565.90000000002</v>
+        <v>134583.63000000003</v>
       </c>
       <c r="F20" s="166">
         <f>'KM-Servicio'!O123</f>
@@ -42091,7 +42091,7 @@
       </c>
       <c r="E21" s="12">
         <f t="shared" si="1"/>
-        <v>145674.10000000003</v>
+        <v>145691.83000000005</v>
       </c>
       <c r="F21" s="166">
         <f>'KM-Servicio'!O130</f>
@@ -42133,7 +42133,7 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="1"/>
-        <v>155456.65000000002</v>
+        <v>155474.38000000003</v>
       </c>
       <c r="F22" s="171">
         <f>'KM-Servicio'!O137</f>
@@ -42175,7 +42175,7 @@
       </c>
       <c r="E23" s="316">
         <f t="shared" si="1"/>
-        <v>164187.67000000001</v>
+        <v>164205.40000000002</v>
       </c>
       <c r="F23" s="317">
         <f>'KM-Servicio'!O144</f>
@@ -42217,7 +42217,7 @@
       </c>
       <c r="E24" s="316">
         <f t="shared" si="1"/>
-        <v>170657.17</v>
+        <v>170674.90000000002</v>
       </c>
       <c r="F24" s="317">
         <f>'KM-Servicio'!O151</f>
@@ -42259,7 +42259,7 @@
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>176350.33000000002</v>
+        <v>176368.06000000003</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O158</f>
@@ -42301,7 +42301,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>185478.76</v>
+        <v>185496.49000000002</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O167</f>
@@ -42343,7 +42343,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>194607.19</v>
+        <v>194624.92</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O176</f>
@@ -42385,7 +42385,7 @@
       </c>
       <c r="E28" s="316">
         <f t="shared" si="1"/>
-        <v>203735.62</v>
+        <v>203753.35</v>
       </c>
       <c r="F28" s="317">
         <f>'KM-Servicio'!O185</f>
@@ -42427,7 +42427,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>212864.05</v>
+        <v>212881.78</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O194</f>
@@ -42469,7 +42469,7 @@
       </c>
       <c r="E30" s="316">
         <f t="shared" si="1"/>
-        <v>221992.47999999998</v>
+        <v>222010.21</v>
       </c>
       <c r="F30" s="317">
         <f>'KM-Servicio'!O203</f>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="E31" s="316">
         <f t="shared" si="1"/>
-        <v>228609.59999999998</v>
+        <v>228627.33</v>
       </c>
       <c r="F31" s="317">
         <f>'KM-Servicio'!O212</f>
@@ -42611,15 +42611,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>228609.59999999998</v>
+        <v>228627.33</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>3266840.2899999996</v>
+        <v>3267088.5100000007</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>95.750428298246973</v>
+        <v>95.76217188663189</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -42631,7 +42631,7 @@
       </c>
       <c r="I36" s="169">
         <f>SUM(I4:I34)</f>
-        <v>18128741.280000001</v>
+        <v>18130147.269000001</v>
       </c>
       <c r="J36" s="30"/>
       <c r="K36" s="168"/>
@@ -42663,12 +42663,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="367" t="s">
+      <c r="A3" s="371" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="368"/>
-      <c r="C3" s="368"/>
-      <c r="D3" s="369"/>
+      <c r="B3" s="372"/>
+      <c r="C3" s="372"/>
+      <c r="D3" s="373"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -42814,12 +42814,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="370" t="s">
+      <c r="A13" s="374" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="371"/>
-      <c r="C13" s="371"/>
-      <c r="D13" s="372"/>
+      <c r="B13" s="375"/>
+      <c r="C13" s="375"/>
+      <c r="D13" s="376"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -42866,8 +42866,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="376"/>
-      <c r="H16" s="376"/>
+      <c r="G16" s="370"/>
+      <c r="H16" s="370"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -42882,8 +42882,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="376"/>
-      <c r="H17" s="376"/>
+      <c r="G17" s="370"/>
+      <c r="H17" s="370"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -42898,8 +42898,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="376"/>
-      <c r="H18" s="376"/>
+      <c r="G18" s="370"/>
+      <c r="H18" s="370"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -42913,8 +42913,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="376"/>
-      <c r="H19" s="376"/>
+      <c r="G19" s="370"/>
+      <c r="H19" s="370"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -42928,8 +42928,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="376"/>
-      <c r="H20" s="376"/>
+      <c r="G20" s="370"/>
+      <c r="H20" s="370"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -42943,8 +42943,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="376"/>
-      <c r="H21" s="376"/>
+      <c r="G21" s="370"/>
+      <c r="H21" s="370"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -42969,9 +42969,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="373"/>
-      <c r="C23" s="374"/>
-      <c r="D23" s="375"/>
+      <c r="B23" s="377"/>
+      <c r="C23" s="378"/>
+      <c r="D23" s="379"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -42983,10 +42983,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="370"/>
-      <c r="B24" s="371"/>
-      <c r="C24" s="371"/>
-      <c r="D24" s="372"/>
+      <c r="A24" s="374"/>
+      <c r="B24" s="375"/>
+      <c r="C24" s="375"/>
+      <c r="D24" s="376"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -43099,9 +43099,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="373"/>
-      <c r="C34" s="374"/>
-      <c r="D34" s="375"/>
+      <c r="B34" s="377"/>
+      <c r="C34" s="378"/>
+      <c r="D34" s="379"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -43234,17 +43234,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43252,6 +43252,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -43498,15 +43507,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -43528,13 +43528,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6CAE7A2-8E0E-423B-9141-5C6F416F96EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0F0025A-7FBD-41CA-948E-842EDA2D5133}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0F0025A-7FBD-41CA-948E-842EDA2D5133}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6CAE7A2-8E0E-423B-9141-5C6F416F96EB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C89A31A4-B059-4FF4-9E6B-ACAC8BAF1913}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C89A31A4-B059-4FF4-9E6B-ACAC8BAF1913}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>